--- a/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/01_CMP1 - Müşteri Şartları ve Belgelendirme/EKG-YNT-LST-13_stellantis_nsa_hazirlik_ve_kanit_takip_cizelgesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/01_Kurumsal Yönetim - Tesis/01_CMP1 - Müşteri Şartları ve Belgelendirme/EKG-YNT-LST-13_stellantis_nsa_hazirlik_ve_kanit_takip_cizelgesi.xlsx
@@ -887,7 +887,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-13&amp;C&amp;"Arial,Regular"&amp;11Stellantis NSA Hazırlık ve Kanıt Takip Çizelgesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 15.09.2026
+Revizyon nedeni: Yanlış NIST kapsamı kaldırıldı; belge Stellantis NSA kaynak ve saha kanıtı takibine dönüştürüldü.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>